--- a/output/Data and Chart Outputs/ghana_capacity_annual.xlsx
+++ b/output/Data and Chart Outputs/ghana_capacity_annual.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,12 +63,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -813,7 +814,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -936,7 +936,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B3" t="n">
@@ -965,7 +965,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B4" t="n">
@@ -994,7 +994,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B5" t="n">
@@ -1023,7 +1023,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B6" t="n">
